--- a/artfynd/Trollberget artfynd.xlsx
+++ b/artfynd/Trollberget artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16944827</v>
+        <v>16944551</v>
       </c>
       <c r="B2" t="n">
-        <v>91541</v>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>677546</v>
+        <v>677057</v>
       </c>
       <c r="R2" t="n">
-        <v>7123143</v>
+        <v>7123784</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -767,9 +767,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>låga</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # låga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,32 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16944757</v>
+        <v>16944838</v>
       </c>
       <c r="B3" t="n">
-        <v>80083</v>
+        <v>91893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>677428</v>
+        <v>677083</v>
       </c>
       <c r="R3" t="n">
-        <v>7123324</v>
+        <v>7123933</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,17 +876,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -899,32 +904,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16944884</v>
+        <v>16944759</v>
       </c>
       <c r="B4" t="n">
-        <v>79987</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>677423</v>
+        <v>677051</v>
       </c>
       <c r="R4" t="n">
-        <v>7123318</v>
+        <v>7123797</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,17 +988,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16944992</v>
+        <v>16944991</v>
       </c>
       <c r="B5" t="n">
-        <v>80112</v>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>677434</v>
+        <v>677051</v>
       </c>
       <c r="R5" t="n">
-        <v>7123449</v>
+        <v>7123797</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,32 +1128,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16945126</v>
+        <v>16944933</v>
       </c>
       <c r="B6" t="n">
-        <v>79012</v>
+        <v>91920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677523</v>
+        <v>677086</v>
       </c>
       <c r="R6" t="n">
-        <v>7123207</v>
+        <v>7124173</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,6 +1209,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1220,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16945081</v>
+        <v>16944828</v>
       </c>
       <c r="B7" t="n">
-        <v>91245</v>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>677697</v>
+        <v>677572</v>
       </c>
       <c r="R7" t="n">
-        <v>7123661</v>
+        <v>7123128</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1332,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16945011</v>
+        <v>16945080</v>
       </c>
       <c r="B8" t="n">
-        <v>91265</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>677259</v>
+        <v>677522</v>
       </c>
       <c r="R8" t="n">
-        <v>7124159</v>
+        <v>7123122</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1416,17 +1436,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1444,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16944758</v>
+        <v>16945126</v>
       </c>
       <c r="B9" t="n">
-        <v>80083</v>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>677091</v>
+        <v>677523</v>
       </c>
       <c r="R9" t="n">
-        <v>7124184</v>
+        <v>7123207</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,21 +1545,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1556,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16944514</v>
+        <v>56606158</v>
       </c>
       <c r="B10" t="n">
-        <v>91263</v>
+        <v>89292</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,13 +1596,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>677569</v>
+        <v>677527</v>
       </c>
       <c r="R10" t="n">
-        <v>7123132</v>
+        <v>7123185</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1637,63 +1642,48 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16944883</v>
+        <v>16944827</v>
       </c>
       <c r="B11" t="n">
-        <v>79987</v>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>677424</v>
+        <v>677546</v>
       </c>
       <c r="R11" t="n">
-        <v>7123381</v>
+        <v>7123143</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1752,17 +1742,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1780,32 +1770,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>16944919</v>
+        <v>16944882</v>
       </c>
       <c r="B12" t="n">
-        <v>91195</v>
+        <v>80336</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>112</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1815,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>677215</v>
+        <v>677150</v>
       </c>
       <c r="R12" t="n">
-        <v>7124121</v>
+        <v>7124038</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1864,17 +1854,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1892,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>16944993</v>
+        <v>16944883</v>
       </c>
       <c r="B13" t="n">
-        <v>80112</v>
+        <v>80336</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,21 +1893,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1927,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>677192</v>
+        <v>677424</v>
       </c>
       <c r="R13" t="n">
-        <v>7123970</v>
+        <v>7123381</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1976,17 +1966,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2004,32 +1994,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>16945079</v>
+        <v>16944884</v>
       </c>
       <c r="B14" t="n">
-        <v>91245</v>
+        <v>80336</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2039,10 +2029,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>677170</v>
+        <v>677423</v>
       </c>
       <c r="R14" t="n">
-        <v>7124258</v>
+        <v>7123318</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2088,17 +2078,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2116,10 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16944759</v>
+        <v>16944757</v>
       </c>
       <c r="B15" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,10 +2141,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>677051</v>
+        <v>677428</v>
       </c>
       <c r="R15" t="n">
-        <v>7123797</v>
+        <v>7123324</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2200,17 +2190,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2228,50 +2218,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16944352</v>
+        <v>16944760</v>
       </c>
       <c r="B16" t="n">
-        <v>4869</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101675</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Trollberget, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>677158</v>
+        <v>677434</v>
       </c>
       <c r="R16" t="n">
-        <v>7123949</v>
+        <v>7123449</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2317,22 +2302,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>bark/ved</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Populus tremula # bark/ved</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2350,10 +2330,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16944882</v>
+        <v>16944992</v>
       </c>
       <c r="B17" t="n">
-        <v>79987</v>
+        <v>80461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2361,21 +2341,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2385,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>677150</v>
+        <v>677434</v>
       </c>
       <c r="R17" t="n">
-        <v>7124038</v>
+        <v>7123449</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2434,17 +2414,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2462,32 +2442,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16944551</v>
+        <v>16944993</v>
       </c>
       <c r="B18" t="n">
-        <v>91259</v>
+        <v>80461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2497,10 +2477,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>677057</v>
+        <v>677192</v>
       </c>
       <c r="R18" t="n">
-        <v>7123784</v>
+        <v>7123970</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2546,22 +2526,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>låga</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies # låga</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2579,10 +2554,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>16944881</v>
+        <v>16944422</v>
       </c>
       <c r="B19" t="n">
-        <v>79987</v>
+        <v>80467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2590,21 +2565,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2614,10 +2589,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>677175</v>
+        <v>677428</v>
       </c>
       <c r="R19" t="n">
-        <v>7124063</v>
+        <v>7123324</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2663,17 +2638,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2691,45 +2666,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>16944828</v>
+        <v>16944352</v>
       </c>
       <c r="B20" t="n">
-        <v>91541</v>
+        <v>4872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>101675</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Trollberget, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>677572</v>
+        <v>677158</v>
       </c>
       <c r="R20" t="n">
-        <v>7123128</v>
+        <v>7123949</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2775,17 +2755,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>bark/ved</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula # bark/ved</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2803,32 +2788,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>16944423</v>
+        <v>16944919</v>
       </c>
       <c r="B21" t="n">
-        <v>80118</v>
+        <v>91859</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2838,10 +2823,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>677091</v>
+        <v>677215</v>
       </c>
       <c r="R21" t="n">
-        <v>7124184</v>
+        <v>7124121</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2887,17 +2872,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2915,10 +2900,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16944760</v>
+        <v>16945079</v>
       </c>
       <c r="B22" t="n">
-        <v>80083</v>
+        <v>91909</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,21 +2911,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2950,10 +2935,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>677434</v>
+        <v>677170</v>
       </c>
       <c r="R22" t="n">
-        <v>7123449</v>
+        <v>7124258</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2999,17 +2984,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3027,32 +3012,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>16944991</v>
+        <v>16945011</v>
       </c>
       <c r="B23" t="n">
-        <v>80112</v>
+        <v>91930</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3062,10 +3047,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>677051</v>
+        <v>677259</v>
       </c>
       <c r="R23" t="n">
-        <v>7123797</v>
+        <v>7124159</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3111,17 +3096,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3139,32 +3124,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>56606158</v>
+        <v>16944881</v>
       </c>
       <c r="B24" t="n">
-        <v>88654</v>
+        <v>80336</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3174,13 +3159,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>677527</v>
+        <v>677175</v>
       </c>
       <c r="R24" t="n">
-        <v>7123185</v>
+        <v>7124063</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3220,48 +3205,63 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>16944422</v>
+        <v>16944758</v>
       </c>
       <c r="B25" t="n">
-        <v>80118</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3271,10 +3271,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>677428</v>
+        <v>677091</v>
       </c>
       <c r="R25" t="n">
-        <v>7123324</v>
+        <v>7124184</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3320,17 +3320,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3348,32 +3348,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>16945080</v>
+        <v>16944423</v>
       </c>
       <c r="B26" t="n">
-        <v>91245</v>
+        <v>80467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>677522</v>
+        <v>677091</v>
       </c>
       <c r="R26" t="n">
-        <v>7123122</v>
+        <v>7124184</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3432,17 +3432,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3460,32 +3460,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>16944933</v>
+        <v>16945081</v>
       </c>
       <c r="B27" t="n">
-        <v>91256</v>
+        <v>91909</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>677086</v>
+        <v>677697</v>
       </c>
       <c r="R27" t="n">
-        <v>7124173</v>
+        <v>7123661</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3544,17 +3544,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3569,118 +3569,6 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>16944838</v>
-      </c>
-      <c r="B28" t="n">
-        <v>91229</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>4660</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Rävticka</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Inocutis rheades</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Trollberget, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>677083</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7123933</v>
-      </c>
-      <c r="S28" t="n">
-        <v>5</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Örträsk</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2014-09-25</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2014-09-25</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
